--- a/product-definitions/spreadsheet/h2-concentration.xlsx
+++ b/product-definitions/spreadsheet/h2-concentration.xlsx
@@ -174,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -208,11 +208,6 @@
     <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -303,7 +298,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
@@ -1903,7 +1898,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="8" t="s">
         <v>19</v>
@@ -1915,7 +1910,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="8" t="s">
         <v>20</v>
@@ -1927,7 +1922,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
@@ -1939,7 +1934,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
@@ -1951,7 +1946,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8" t="s">
         <v>25</v>
@@ -1963,7 +1958,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="9" t="s">
         <v>26</v>
@@ -1975,7 +1970,7 @@
       </c>
       <c r="F26" s="8"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8" t="s">
         <v>28</v>
@@ -1987,7 +1982,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="17" t="s">
         <v>30</v>
@@ -1999,7 +1994,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -2007,7 +2002,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>35</v>
       </c>
@@ -2017,7 +2012,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8" t="s">
         <v>10</v>
@@ -2029,7 +2024,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="8" t="s">
         <v>12</v>
@@ -2041,7 +2036,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="9" t="s">
         <v>2</v>
@@ -2053,7 +2048,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="8"/>
       <c r="B34" s="8" t="s">
         <v>19</v>
@@ -2065,7 +2060,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="8" t="s">
         <v>20</v>
@@ -2077,7 +2072,7 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="8" t="s">
         <v>22</v>
@@ -2089,7 +2084,7 @@
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>23</v>
@@ -2101,7 +2096,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="8"/>
       <c r="B38" s="8" t="s">
         <v>25</v>
@@ -2113,7 +2108,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="8"/>
       <c r="B39" s="9" t="s">
         <v>26</v>
@@ -2125,7 +2120,7 @@
       </c>
       <c r="F39" s="8"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="8" t="s">
         <v>28</v>
@@ -2137,7 +2132,7 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="8"/>
       <c r="B41" s="17" t="s">
         <v>30</v>
@@ -2149,7 +2144,7 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2157,7 +2152,7 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="7" t="s">
         <v>38</v>
       </c>
@@ -2167,7 +2162,7 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="8" t="s">
         <v>10</v>
@@ -2179,7 +2174,7 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="8" t="s">
         <v>12</v>
@@ -2191,7 +2186,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="9"/>
       <c r="B46" s="9" t="s">
         <v>2</v>
@@ -2203,7 +2198,7 @@
       <c r="E46" s="6"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="8" t="s">
         <v>19</v>
@@ -2215,7 +2210,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="8" t="s">
         <v>20</v>
@@ -2227,7 +2222,7 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
       <c r="B49" s="8" t="s">
         <v>22</v>
@@ -2239,7 +2234,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="8"/>
       <c r="B50" s="8" t="s">
         <v>23</v>
@@ -2251,7 +2246,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
         <v>25</v>
@@ -2263,7 +2258,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8"/>
       <c r="B52" s="9" t="s">
         <v>26</v>
@@ -2275,7 +2270,7 @@
       </c>
       <c r="F52" s="8"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8"/>
       <c r="B53" s="8" t="s">
         <v>28</v>
@@ -2287,7 +2282,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="8"/>
       <c r="B54" s="17" t="s">
         <v>30</v>
@@ -2299,17 +2294,17 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="C55" s="22"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="23" t="s">
         <v>41</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="24"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
         <v>10</v>
@@ -2318,7 +2313,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
         <v>12</v>
@@ -2327,7 +2322,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>2</v>
@@ -2336,14 +2331,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="25"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>20</v>
@@ -2352,7 +2347,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="8" t="s">
         <v>44</v>
@@ -2361,7 +2356,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="6" t="s">
         <v>46</v>
